--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="O71" s="9" t="n">
-        <v>0.028191</v>
+        <v>0.027629</v>
       </c>
       <c r="P71" s="11" t="inlineStr">
         <is>
@@ -5455,7 +5455,9 @@
           <t>estimado</t>
         </is>
       </c>
-      <c r="O72" s="6" t="n"/>
+      <c r="O72" s="6" t="n">
+        <v>0.033585</v>
+      </c>
       <c r="P72" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="O72" s="6" t="n">
-        <v>0.033585</v>
+        <v>0.03408</v>
       </c>
       <c r="P72" s="8" t="inlineStr">
         <is>

--- a/downloads/indicadores/IOAE/IOAE_datos.xlsx
+++ b/downloads/indicadores/IOAE/IOAE_datos.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S72"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf · Fecha de publicación: 20 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf · Fecha de publicación: 20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S21" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S23" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S27" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="R35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="R37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S37" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="R39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S39" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="R41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S41" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="R43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S43" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="R45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S45" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3645,12 +3645,12 @@
       </c>
       <c r="R47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S47" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="R49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S49" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="R52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="R53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S53" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="R55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S55" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4302,12 +4302,12 @@
       </c>
       <c r="R56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="R57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S57" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="R58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="R59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S59" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="R61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S61" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="R62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="R63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S63" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="R64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="R65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S65" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="R67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S67" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="R68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="R69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S69" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="R70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="R71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S71" s="11" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5470,12 +5470,156 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr">
         <is>
-          <t>20 de agosto de 2026</t>
+          <t>20 de octubre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>22 sep 2026</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>estimado</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="n">
+        <v>0.033335</v>
+      </c>
+      <c r="P73" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="Q73" s="11" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="R73" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
+        </is>
+      </c>
+      <c r="S73" s="11" t="inlineStr">
+        <is>
+          <t>20 de octubre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>20 oct 2026</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>estimado</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="R74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_10.pdf</t>
+        </is>
+      </c>
+      <c r="S74" s="8" t="inlineStr">
+        <is>
+          <t>20 de octubre de 2026</t>
         </is>
       </c>
     </row>
